--- a/tame_output/ON/bt/strategyON_20240801.xlsx
+++ b/tame_output/ON/bt/strategyON_20240801.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>68.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-80.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.0%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.4%</t>
+          <t>-684.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-203.9%</t>
+          <t>-205.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.9%</t>
+          <t>-230.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-68.5%</t>
+          <t>-69.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2041"/>
+  <dimension ref="A1:G2042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807206190640606</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48504,6 +48504,29 @@
       </c>
       <c r="G2041" t="n">
         <v>3.775561208894822</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="2" t="n">
+        <v>45504</v>
+      </c>
+      <c r="B2042" t="n">
+        <v>3.776807407941017</v>
+      </c>
+      <c r="C2042" t="n">
+        <v>3.802592933950636</v>
+      </c>
+      <c r="D2042" t="n">
+        <v>-5.229459345393394</v>
+      </c>
+      <c r="E2042" t="n">
+        <v>1.710452771479531</v>
+      </c>
+      <c r="F2042" t="n">
+        <v>-0.06572800277182095</v>
+      </c>
+      <c r="G2042" t="n">
+        <v>3.763156132287544</v>
       </c>
     </row>
   </sheetData>
